--- a/product_surveys/047_skincare_product_trust_factor_survey--product_surveys.xlsx
+++ b/product_surveys/047_skincare_product_trust_factor_survey--product_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -707,12 +707,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -774,12 +774,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'not_sure'}</t>
+          <t>not_sure</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Not sure'}</t>
+          <t>Not sure</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_not_sure'}</t>
+          <t>somewhat_not_sure</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat not sure'}</t>
+          <t>Somewhat not sure</t>
         </is>
       </c>
     </row>
@@ -808,12 +808,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat'}</t>
+          <t>somewhat</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat'}</t>
+          <t>Somewhat</t>
         </is>
       </c>
     </row>
@@ -825,53 +825,53 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat'}</t>
+          <t>very</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat'}</t>
+          <t>Very</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>product_trust_level_choices</t>
+          <t>skincare_product_trust_factors_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'very'}</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Very'}</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>product_trust_level_choices</t>
+          <t>skincare_product_trust_factors_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'very'}</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Very'}</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>skincare_product_trust_factors_2_choices</t>
+          <t>skincare_product_trust_factors_3_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -888,7 +888,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>skincare_product_trust_factors_2_choices</t>
+          <t>skincare_product_trust_factors_3_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -905,7 +905,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>skincare_product_trust_factors_3_choices</t>
+          <t>skincare_product_trust_factors_4_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -922,7 +922,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>skincare_product_trust_factors_3_choices</t>
+          <t>skincare_product_trust_factors_4_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -939,7 +939,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>skincare_product_trust_factors_4_choices</t>
+          <t>skincare_product_trust_factors_5_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -956,7 +956,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>skincare_product_trust_factors_4_choices</t>
+          <t>skincare_product_trust_factors_5_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -965,40 +965,6 @@
         </is>
       </c>
       <c r="C15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>skincare_product_trust_factors_5_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>skincare_product_trust_factors_5_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
         <is>
           <t>No</t>
         </is>
